--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ABDE633-BA19-4B34-B05C-4D643028B7D2}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15436C0D-D158-4DA0-A36C-82A1B55F9FDA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,6 +177,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
@@ -598,9 +602,11 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
       <c r="F5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15436C0D-D158-4DA0-A36C-82A1B55F9FDA}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95927D2C-9AA7-468C-99F7-B0608D4DD13D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,7 +601,9 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
       <c r="E5" s="3">
         <v>1</v>
       </c>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95927D2C-9AA7-468C-99F7-B0608D4DD13D}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C354986-304C-4FA7-B75A-9BBBD42874BA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -65,16 +65,13 @@
 Long</t>
   </si>
   <si>
-    <t>1. Ai là người giúp đỡ, hỗ trợ bạn nhiều nhất trong thời gian vừa qua?</t>
-  </si>
-  <si>
-    <t>2. Ai là người làm việc hiệu quả và đóng góp nhiều nhất cho Dự án?</t>
-  </si>
-  <si>
-    <t>3. Ai là người đang gây khó khăn cho bạn trong công tác phối hợp?</t>
-  </si>
-  <si>
-    <t>4. Ai là người bạn cảm thấy cần nỗ lực và chủ động hơn nữa để đóng góp cho dự án?</t>
+    <t>Tiêu chí 01: Ai là người giúp đỡ, hỗ trợ bạn nhiều nhất trong Tuần làm việc vừa qua.</t>
+  </si>
+  <si>
+    <t>Tiêu chí 02: Ai là người làm việc hiệu quả và đóng góp nhiều nhất trong Tuần làm việc vừa qua.</t>
+  </si>
+  <si>
+    <t>Tiêu chí 03: Ai là người đang gây khó khăn cho bạn trong công tác phối hợp trong Tuần làm việc vừa qua.</t>
   </si>
 </sst>
 </file>
@@ -177,10 +174,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,7 +464,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="41.9296875" style="1" customWidth="1"/>
@@ -586,37 +579,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
       <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C354986-304C-4FA7-B75A-9BBBD42874BA}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2589443-E7C5-4661-BEDD-F0741BCB23E6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -601,4 +602,150 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFAB33A2-E40A-4D9D-8E8C-7595D6E48AC6}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="1" customWidth="1"/>
+    <col min="2" max="11" width="13" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5</v>
+      </c>
+      <c r="I2" s="3">
+        <v>7</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3">
+        <v>5</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2589443-E7C5-4661-BEDD-F0741BCB23E6}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E19183-C165-4AD7-A600-A45B2C7E02F5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -602,150 +601,4 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFAB33A2-E40A-4D9D-8E8C-7595D6E48AC6}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="41.9296875" style="1" customWidth="1"/>
-    <col min="2" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.06640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2" s="3">
-        <v>2</v>
-      </c>
-      <c r="H2" s="3">
-        <v>5</v>
-      </c>
-      <c r="I2" s="3">
-        <v>7</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>3</v>
-      </c>
-      <c r="H3" s="3">
-        <v>4</v>
-      </c>
-      <c r="I3" s="3">
-        <v>5</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
-        <v>2</v>
-      </c>
-      <c r="K4" s="3"/>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E19183-C165-4AD7-A600-A45B2C7E02F5}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A10B4C9F-A10B-4513-988C-DD018B11DDE5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -601,4 +602,148 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B15920-8FDF-4E54-A5B7-00639EB77119}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="1" customWidth="1"/>
+    <col min="2" max="11" width="13" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5</v>
+      </c>
+      <c r="I2" s="3">
+        <v>5</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3">
+        <v>4</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A10B4C9F-A10B-4513-988C-DD018B11DDE5}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E41EF57A-4181-4AFB-839F-D0B04030E7C1}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Phiếu Đánh Giá Tổng Hợp Tuần 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Phiếu Đánh Giá Tuần 2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -73,13 +73,16 @@
   </si>
   <si>
     <t>Tiêu chí 03: Ai là người đang gây khó khăn cho bạn trong công tác phối hợp trong Tuần làm việc vừa qua.</t>
+  </si>
+  <si>
+    <t>Tiêu chí 04: Ai là người bạn cảm thấy cần nỗ lực và chủ động hơn nữa để đóng góp cho dự án</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,21 +91,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -121,12 +118,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -139,27 +151,29 @@
       <top style="thin">
         <color rgb="FFBFBFBF"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,15 +479,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="41.9296875" style="1" customWidth="1"/>
-    <col min="2" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -508,94 +522,109 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4">
         <v>3</v>
       </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2" s="3">
-        <v>2</v>
-      </c>
-      <c r="H2" s="3">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3">
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
         <v>6</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
+      <c r="J2" s="4"/>
+      <c r="K2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>2</v>
-      </c>
-      <c r="H3" s="3">
-        <v>4</v>
-      </c>
-      <c r="I3" s="3">
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4">
         <v>6</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3"/>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="6"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -605,19 +634,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B15920-8FDF-4E54-A5B7-00639EB77119}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA9129E-5771-4CC6-95DD-34563BC6F952}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="41.9296875" style="1" customWidth="1"/>
-    <col min="2" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -652,94 +681,109 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4">
         <v>3</v>
       </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4">
         <v>5</v>
       </c>
-      <c r="G2" s="3">
+      <c r="F3" s="4">
+        <v>6</v>
+      </c>
+      <c r="G3" s="4">
+        <v>7</v>
+      </c>
+      <c r="H3" s="4">
+        <v>8</v>
+      </c>
+      <c r="I3" s="4">
+        <v>9</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
         <v>3</v>
       </c>
-      <c r="H2" s="3">
-        <v>5</v>
-      </c>
-      <c r="I2" s="3">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3">
+    </row>
+    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
         <v>3</v>
       </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>2</v>
-      </c>
-      <c r="H3" s="3">
-        <v>6</v>
-      </c>
-      <c r="I3" s="3">
-        <v>4</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
-        <v>2</v>
-      </c>
-      <c r="K4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6">
+        <v>2</v>
+      </c>
+      <c r="K5" s="6"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>

--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E41EF57A-4181-4AFB-839F-D0B04030E7C1}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD01C330-52C3-40A5-B60F-38D56F6B504F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Phiếu Đánh Giá Tuần 2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -631,163 +630,4 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA9129E-5771-4CC6-95DD-34563BC6F952}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
-    <col min="2" max="11" width="13" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9.06640625" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4">
-        <v>2</v>
-      </c>
-      <c r="H2" s="4">
-        <v>4</v>
-      </c>
-      <c r="I2" s="4">
-        <v>6</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4">
-        <v>4</v>
-      </c>
-      <c r="E3" s="4">
-        <v>5</v>
-      </c>
-      <c r="F3" s="4">
-        <v>6</v>
-      </c>
-      <c r="G3" s="4">
-        <v>7</v>
-      </c>
-      <c r="H3" s="4">
-        <v>8</v>
-      </c>
-      <c r="I3" s="4">
-        <v>9</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6">
-        <v>2</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6">
-        <v>2</v>
-      </c>
-      <c r="K5" s="6"/>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD01C330-52C3-40A5-B60F-38D56F6B504F}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21F263BE-9518-4E08-9390-0A411615203F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu Đánh Giá Pre-work&amp;Tuần 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Phiếu Đánh Giá Tuần 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t>Các câu hỏi đánh giá</t>
   </si>
@@ -630,4 +631,159 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448980E8-86AA-41A7-8183-196DA736F1AD}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="41.9296875" style="3" customWidth="1"/>
+    <col min="2" max="11" width="13" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="55.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2</v>
+      </c>
+      <c r="I3" s="4">
+        <v>4</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Du_Lieu_Danh_Gia.xlsx
+++ b/Du_Lieu_Danh_Gia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tapdoanxangdau-my.sharepoint.com/personal/hiepnm_petrolimex_com_vn/Documents/01/Tập đoàn/Web đánh giá Dự án/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21F263BE-9518-4E08-9390-0A411615203F}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="8_{A86F4960-6916-4912-9B9B-3FFC93CC16EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99585234-2629-4787-9FD4-D1D99B72176C}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -693,10 +693,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="4">
         <v>4</v>
@@ -729,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4">
         <v>3</v>
@@ -738,7 +738,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4">
